--- a/docs/test-data/sample-movies.xlsx
+++ b/docs/test-data/sample-movies.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Programming\VSCode\MovieCollectionManager\docs\test-data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5731BCCB-FC1A-474E-A057-E57746343917}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E9B02BD6-8285-49C8-BEF0-E2E20A39CDB8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-103" yWindow="-103" windowWidth="33120" windowHeight="18000" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3555" uniqueCount="1728">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3573" uniqueCount="1731">
   <si>
     <t>Title</t>
   </si>
@@ -5223,13 +5223,22 @@
   </si>
   <si>
     <t>Drama|Crime|Action|Superhero</t>
+  </si>
+  <si>
+    <t>Expected Import Failure 1</t>
+  </si>
+  <si>
+    <t>Expected Import Failure 2</t>
+  </si>
+  <si>
+    <t>Expected Import Failure 3</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="10"/>
       <name val="Arial"/>
@@ -5244,6 +5253,10 @@
       <b/>
       <sz val="10"/>
       <color rgb="FFFFFFFF"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="8"/>
       <name val="Arial"/>
     </font>
   </fonts>
@@ -5582,7 +5595,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{42034FD5-E37F-4D1D-B2D1-1EADFF6F6069}">
-  <dimension ref="A1:AA201"/>
+  <dimension ref="A1:AA204"/>
   <sheetFormatPr defaultRowHeight="12.45" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="46.07421875" bestFit="1" customWidth="1"/>
@@ -18689,15 +18702,82 @@
         <v>1727</v>
       </c>
     </row>
+    <row r="202" spans="1:27" ht="15.9" x14ac:dyDescent="0.45">
+      <c r="A202" t="s">
+        <v>1728</v>
+      </c>
+      <c r="B202">
+        <v>2007</v>
+      </c>
+      <c r="C202" t="s">
+        <v>26</v>
+      </c>
+      <c r="D202" t="s">
+        <v>27</v>
+      </c>
+      <c r="E202">
+        <v>0</v>
+      </c>
+      <c r="F202" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="G202" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="H202" s="1" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="203" spans="1:27" ht="15.9" x14ac:dyDescent="0.45">
+      <c r="A203" t="s">
+        <v>1729</v>
+      </c>
+      <c r="B203" t="s">
+        <v>26</v>
+      </c>
+      <c r="C203" t="s">
+        <v>1620</v>
+      </c>
+      <c r="D203" t="s">
+        <v>27</v>
+      </c>
+      <c r="E203" t="s">
+        <v>28</v>
+      </c>
+      <c r="F203" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="G203" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="H203" s="1" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="204" spans="1:27" x14ac:dyDescent="0.3">
+      <c r="A204" t="s">
+        <v>1730</v>
+      </c>
+      <c r="C204" t="s">
+        <v>50</v>
+      </c>
+      <c r="D204" t="s">
+        <v>28</v>
+      </c>
+      <c r="E204" t="s">
+        <v>28</v>
+      </c>
+    </row>
   </sheetData>
+  <phoneticPr fontId="3" type="noConversion"/>
   <dataValidations count="3">
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="C201:E201" xr:uid="{B9F39785-53CD-4914-A03B-595EEAFA8D04}">
       <formula1>Category</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="G201 D201:E201" xr:uid="{8A5396B6-FA61-4746-841A-2036ADAD525E}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="G201:G203 D201:E201" xr:uid="{8A5396B6-FA61-4746-841A-2036ADAD525E}">
       <formula1>YesNo</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H201 F201" xr:uid="{DF5524FB-9018-47D0-B30E-437095B27A4E}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H201:H203 F201:F203" xr:uid="{DF5524FB-9018-47D0-B30E-437095B27A4E}">
       <formula1>MediaType</formula1>
     </dataValidation>
   </dataValidations>

--- a/docs/test-data/sample-movies.xlsx
+++ b/docs/test-data/sample-movies.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Programming\VSCode\MovieCollectionManager\docs\test-data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E9B02BD6-8285-49C8-BEF0-E2E20A39CDB8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{ED688B21-FA4E-4E7A-B808-999AD918ED7F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-103" yWindow="-103" windowWidth="33120" windowHeight="18000" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3573" uniqueCount="1731">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3577" uniqueCount="1733">
   <si>
     <t>Title</t>
   </si>
@@ -5232,6 +5232,12 @@
   </si>
   <si>
     <t>Expected Import Failure 3</t>
+  </si>
+  <si>
+    <t>Test Movie 7</t>
+  </si>
+  <si>
+    <t>Maybe</t>
   </si>
 </sst>
 </file>
@@ -5595,7 +5601,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{42034FD5-E37F-4D1D-B2D1-1EADFF6F6069}">
-  <dimension ref="A1:AA204"/>
+  <dimension ref="A1:AA205"/>
   <sheetFormatPr defaultRowHeight="12.45" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="46.07421875" bestFit="1" customWidth="1"/>
@@ -18768,6 +18774,23 @@
         <v>28</v>
       </c>
     </row>
+    <row r="205" spans="1:27" x14ac:dyDescent="0.3">
+      <c r="A205" t="s">
+        <v>1731</v>
+      </c>
+      <c r="B205">
+        <v>1932</v>
+      </c>
+      <c r="C205" t="s">
+        <v>275</v>
+      </c>
+      <c r="D205" t="s">
+        <v>27</v>
+      </c>
+      <c r="E205" t="s">
+        <v>1732</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="3" type="noConversion"/>
   <dataValidations count="3">

--- a/docs/test-data/sample-movies.xlsx
+++ b/docs/test-data/sample-movies.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Programming\VSCode\MovieCollectionManager\docs\test-data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5731BCCB-FC1A-474E-A057-E57746343917}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{ED688B21-FA4E-4E7A-B808-999AD918ED7F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-103" yWindow="-103" windowWidth="33120" windowHeight="18000" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3555" uniqueCount="1728">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3577" uniqueCount="1733">
   <si>
     <t>Title</t>
   </si>
@@ -5223,13 +5223,28 @@
   </si>
   <si>
     <t>Drama|Crime|Action|Superhero</t>
+  </si>
+  <si>
+    <t>Expected Import Failure 1</t>
+  </si>
+  <si>
+    <t>Expected Import Failure 2</t>
+  </si>
+  <si>
+    <t>Expected Import Failure 3</t>
+  </si>
+  <si>
+    <t>Test Movie 7</t>
+  </si>
+  <si>
+    <t>Maybe</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="10"/>
       <name val="Arial"/>
@@ -5244,6 +5259,10 @@
       <b/>
       <sz val="10"/>
       <color rgb="FFFFFFFF"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="8"/>
       <name val="Arial"/>
     </font>
   </fonts>
@@ -5582,7 +5601,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{42034FD5-E37F-4D1D-B2D1-1EADFF6F6069}">
-  <dimension ref="A1:AA201"/>
+  <dimension ref="A1:AA205"/>
   <sheetFormatPr defaultRowHeight="12.45" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="46.07421875" bestFit="1" customWidth="1"/>
@@ -18689,15 +18708,99 @@
         <v>1727</v>
       </c>
     </row>
+    <row r="202" spans="1:27" ht="15.9" x14ac:dyDescent="0.45">
+      <c r="A202" t="s">
+        <v>1728</v>
+      </c>
+      <c r="B202">
+        <v>2007</v>
+      </c>
+      <c r="C202" t="s">
+        <v>26</v>
+      </c>
+      <c r="D202" t="s">
+        <v>27</v>
+      </c>
+      <c r="E202">
+        <v>0</v>
+      </c>
+      <c r="F202" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="G202" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="H202" s="1" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="203" spans="1:27" ht="15.9" x14ac:dyDescent="0.45">
+      <c r="A203" t="s">
+        <v>1729</v>
+      </c>
+      <c r="B203" t="s">
+        <v>26</v>
+      </c>
+      <c r="C203" t="s">
+        <v>1620</v>
+      </c>
+      <c r="D203" t="s">
+        <v>27</v>
+      </c>
+      <c r="E203" t="s">
+        <v>28</v>
+      </c>
+      <c r="F203" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="G203" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="H203" s="1" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="204" spans="1:27" x14ac:dyDescent="0.3">
+      <c r="A204" t="s">
+        <v>1730</v>
+      </c>
+      <c r="C204" t="s">
+        <v>50</v>
+      </c>
+      <c r="D204" t="s">
+        <v>28</v>
+      </c>
+      <c r="E204" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="205" spans="1:27" x14ac:dyDescent="0.3">
+      <c r="A205" t="s">
+        <v>1731</v>
+      </c>
+      <c r="B205">
+        <v>1932</v>
+      </c>
+      <c r="C205" t="s">
+        <v>275</v>
+      </c>
+      <c r="D205" t="s">
+        <v>27</v>
+      </c>
+      <c r="E205" t="s">
+        <v>1732</v>
+      </c>
+    </row>
   </sheetData>
+  <phoneticPr fontId="3" type="noConversion"/>
   <dataValidations count="3">
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="C201:E201" xr:uid="{B9F39785-53CD-4914-A03B-595EEAFA8D04}">
       <formula1>Category</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="G201 D201:E201" xr:uid="{8A5396B6-FA61-4746-841A-2036ADAD525E}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="G201:G203 D201:E201" xr:uid="{8A5396B6-FA61-4746-841A-2036ADAD525E}">
       <formula1>YesNo</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H201 F201" xr:uid="{DF5524FB-9018-47D0-B30E-437095B27A4E}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H201:H203 F201:F203" xr:uid="{DF5524FB-9018-47D0-B30E-437095B27A4E}">
       <formula1>MediaType</formula1>
     </dataValidation>
   </dataValidations>
